--- a/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4545</v>
+        <v>0.5385</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8193</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.3929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3667</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9601</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6</v>
+        <v>0.4286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4545</v>
+        <v>0.5385</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7817</v>
+        <v>0.8214</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ofereix flexibilitat, escalabilitat i reducció de costos, ja que elimina la necessitat d’infraestructura local pròpia.</t>
+          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.784</v>
+        <v>0.8314</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Aquest microservei incorpora mecanismes de protecció per assegurar la integritat i la confidencialitat de les comunicacions. Concretament, bloqueja qualsevol intent de connexió no autoritzada i aplica determinats protocols de seguretat per prevenir accessos indeguts i possibles vulnerabilitats.</t>
+          <t>This microservice incorporates protection mechanisms to ensure the integrity and confidentiality of communications, blocking any unauthorized connection attempt and applying security protocols to prevent improper access and possible vulnerabilities.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R_48</t>
+          <t>R_48, Security</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8103</v>
+        <v>0.8401</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Això garanteix que la capa de presentació estigui disponible i actualitzada, facilitant el desplegament i reduint la dependència d’elements externs. D’aquesta manera, el portal no només centralitza l’accés, sinó que també assegura la coherència visual i funcional de tot l’ecosistema.</t>
+          <t>This microservice incorporates the necessary binaries for the frontEnd of both the portal itself and the rest of the portal applications, ensuring visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1233,22 +1233,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.837</v>
+        <v>0.857</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1268,135 +1268,307 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Aquesta separació de responsabilitats permet que el client es focalitzi en la presentació i en l’experiència d’usuari, mentre que el servidor se centra en la lògica de negoci, la seguretat, la integritat de les dades i la persistència.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P_01, AU_13, AU_14</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C_05, C_09</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>CF_M05_AD11</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C8" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Permet automatitzar el desplegament, escalat i gestió d’aplicacions que corren en contenidors, executar milers de contenidors en diferents servidors i assegurar alta disponibilitat.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>It allows automating the deployment, scaling, and management of applications running in containers, executing thousands of containers on different servers, and ensuring high availability.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C_06, C_07</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>AU_18, AU_19</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_C06, CF_M05_C07</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>81</v>
       </c>
     </row>
@@ -1411,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,106 +1626,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aquesta estructura permet desenvolupar, desplegar i escalar cada servei de manera autònoma, facilitant el manteniment, la flexibilitat i l’evolució del sistema.</t>
+          <t>Angular applies the MVVM pattern, as its architecture is based on components and services, which is designed for the implementation of user interfaces.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microserveis</t>
+          <t>C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7383</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Angular aplica el patró MVVM (Model-View-ViewModel), ja que la seva arquitectura està basada en components i serveis.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C_02</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD09</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.6614</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Spring Boot organitza el codi seguint el patró a capes amb les quals se separen responsabilitats: la capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C_09</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7294</v>
+        <v>0.726</v>
       </c>
     </row>
   </sheetData>
@@ -1610,59 +1712,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7383</v>
+        <v>0.7897</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1670,139 +1772,139 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7561</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6665</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8349</v>
+        <v>0.726</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7174</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6593</v>
+        <v>0.767</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval.xlsx
@@ -450,13 +450,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5385</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.8759</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -492,8 +494,10 @@
           <t>exact match on normalised text</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.3929</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -512,11 +516,15 @@
           <t>embedding cosine &gt;= 0.75</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.9701</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -530,8 +538,10 @@
           <t>page-number sets overlap</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0.4286</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +592,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +602,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +612,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +622,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +632,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +642,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +736,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +765,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +802,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +839,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,718 +871,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>LLM_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>GT_ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rationale_similarity</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>source_matched</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>source_gt_total</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>source_llm_total</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>source_accuracy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>source_mean_similarity</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>element_matched</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>element_gt_total</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>element_llm_total</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>element_accuracy</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>element_mean_similarity</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>LLM_rationale</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>LLM_architecturalDecisionSource</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>LLM_architecturalElementIds</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>LLM_pageNumber</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>GT_rationale</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>GT_architecturalDecisionSource</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>GT_architecturalElementIds</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>GT_pageNumber</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Tecnologia cloud</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>CF_M05_P05</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8314</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>This microservice incorporates protection mechanisms to ensure the integrity and confidentiality of communications, blocking any unauthorized connection attempt and applying security protocols to prevent improper access and possible vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R_48, Security</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>*CF_M05_C11</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8401</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8804</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This microservice incorporates the necessary binaries for the frontEnd of both the portal itself and the rest of the portal applications, ensuring visual and functional coherence of the entire ecosystem.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>C_01</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8651</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>C_05, C_09</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD11</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.9916</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>It allows automating the deployment, scaling, and management of applications running in containers, executing thousands of containers on different servers, and ensuring high availability.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>C_06, C_07</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>AU_18, AU_19</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1583,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,27 +927,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services, which is designed for the implementation of user interfaces.</t>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA) [19] que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_02</t>
+          <t>R_42, C_05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_13, AU_22, P_03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60, 61</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1655,7 +956,112 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.726</v>
+        <v>0.6991000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pel servidor s’ha utilitzat Spring Boot, que proporciona una plataforma per exposar una API REST [20].</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_05, C_06, C_09</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6472</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fetús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R_43, R_44, R_45, R_46, C_06, C_07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6856</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Low price and previous company use</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6961000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,199 +1118,430 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7897</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.665</v>
+        <v>0.6165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8676</v>
+        <v>0.6375999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.726</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7173</v>
+        <v>0.5933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>*CF_M05_C15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6637</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6837</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6222</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E14" t="n">
         <v>82</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.767</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6818</v>
       </c>
     </row>
   </sheetData>
